--- a/data/trans_camb/P05B_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P05B_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>-0,98</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,44</t>
+          <t>-3,55</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-2,43</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; -0,34</t>
+          <t>-2,95; -0,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,06; -0,37</t>
+          <t>-3,05; -0,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,98</t>
+          <t>-2,31; 0,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,22; -2,52</t>
+          <t>-5,24; -2,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,21; -1,02</t>
+          <t>-4,16; -0,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,95; -2,15</t>
+          <t>-4,9; -2,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; -1,91</t>
+          <t>-3,86; -1,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; -1,14</t>
+          <t>-3,27; -1,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; -1,22</t>
+          <t>-3,45; -1,37</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-22,56%</t>
+          <t>-32,18%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-66,6%</t>
+          <t>-68,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-53,17%</t>
+          <t>-57,33%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-75,05; -10,86</t>
+          <t>-76,17; -9,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-79,77; -12,26</t>
+          <t>-79,31; -12,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,13; 44,8</t>
+          <t>-63,95; 38,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-86,07; -54,9</t>
+          <t>-86,17; -57,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,48; -21,42</t>
+          <t>-69,81; -19,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,74; -43,58</t>
+          <t>-80,79; -50,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-79,29; -52,04</t>
+          <t>-79,12; -51,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,21; -29,16</t>
+          <t>-67,69; -29,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,93; -31,53</t>
+          <t>-71,1; -38,25</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,45</t>
+          <t>-3,37</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,84</t>
+          <t>-2,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; -0,2</t>
+          <t>-2,28; -0,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; -0,56</t>
+          <t>-2,44; -0,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; -1,41</t>
+          <t>-3,22; -1,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -1,09</t>
+          <t>-3,54; -1,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; -1,1</t>
+          <t>-3,63; -1,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,58; -2,38</t>
+          <t>-4,46; -2,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; -1,06</t>
+          <t>-2,64; -1,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; -1,11</t>
+          <t>-2,62; -1,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; -2,08</t>
+          <t>-3,51; -2,12</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-79,48%</t>
+          <t>-79,35%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-78,63%</t>
+          <t>-76,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-78,88%</t>
+          <t>-77,73%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-66,46; -7,79</t>
+          <t>-65,82; -11,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-69,63; -18,19</t>
+          <t>-69,79; -22,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-90,83; -59,4</t>
+          <t>-89,94; -60,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-70,2; -30,27</t>
+          <t>-68,9; -26,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,55; -29,96</t>
+          <t>-69,31; -30,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,15; -65,48</t>
+          <t>-85,47; -62,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,66; -33,5</t>
+          <t>-63,53; -32,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,72; -34,85</t>
+          <t>-64,02; -34,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-85,73; -68,09</t>
+          <t>-84,74; -67,77</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>-1,2</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,59</t>
+          <t>-2,67</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,85</t>
+          <t>-1,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,45</t>
+          <t>-2,72; 1,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,21</t>
+          <t>-3,77; 0,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,65</t>
+          <t>-3,34; 0,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,41; -1,33</t>
+          <t>-5,61; -1,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,06; -0,88</t>
+          <t>-4,92; -0,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; -0,45</t>
+          <t>-5,11; -0,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,39; -0,57</t>
+          <t>-3,52; -0,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,65; -0,71</t>
+          <t>-3,73; -0,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,28; -0,54</t>
+          <t>-3,34; -0,61</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-40,1%</t>
+          <t>-40,01%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-59,85%</t>
+          <t>-61,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-51,14%</t>
+          <t>-52,13%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-69,48; 79,52</t>
+          <t>-67,38; 92,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-88,54; 22,29</t>
+          <t>-87,88; 33,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,47; 45,72</t>
+          <t>-75,4; 33,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-92,2; -39,87</t>
+          <t>-92,43; -33,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-85,22; -22,54</t>
+          <t>-85,31; -11,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,08; -11,33</t>
+          <t>-80,68; -21,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-74,99; -16,24</t>
+          <t>-77,65; -13,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,51; -21,54</t>
+          <t>-79,89; -28,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,27; -17,25</t>
+          <t>-71,67; -17,21</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,44</t>
+          <t>-3,41</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,66</t>
+          <t>-2,65</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; -0,58</t>
+          <t>-2,05; -0,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; -0,84</t>
+          <t>-2,24; -0,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; -1,18</t>
+          <t>-2,61; -1,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -2,2</t>
+          <t>-3,95; -2,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,41; -1,65</t>
+          <t>-3,51; -1,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,28; -2,64</t>
+          <t>-4,23; -2,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -1,6</t>
+          <t>-2,75; -1,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; -1,47</t>
+          <t>-2,63; -1,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,21; -2,11</t>
+          <t>-3,17; -2,13</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-63,38%</t>
+          <t>-63,4%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-73,42%</t>
+          <t>-72,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-69,59%</t>
+          <t>-69,14%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-59,21; -19,77</t>
+          <t>-61,4; -20,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-68,35; -32,72</t>
+          <t>-67,21; -32,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-75,98; -44,89</t>
+          <t>-76,01; -44,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-74,85; -52,66</t>
+          <t>-74,66; -52,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-65,23; -39,9</t>
+          <t>-65,14; -37,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,17; -63,39</t>
+          <t>-80,07; -63,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-65,55; -46,35</t>
+          <t>-65,89; -45,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,05; -40,36</t>
+          <t>-63,04; -42,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-76,4; -60,63</t>
+          <t>-75,76; -60,71</t>
         </is>
       </c>
     </row>
